--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Jernbanestatistikk_2012_2024.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Jernbanestatistikk_2012_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/kjetil_gunnerud_kristoffersen_vestfoldfylke_no/Documents/Dokumenter/GitHub2/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="677" documentId="8_{97E84CCC-6234-465C-AE6C-762AAC589669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6238E16A-0D3B-4F7B-B776-A7E8BEEEFBAA}"/>
+  <xr:revisionPtr revIDLastSave="687" documentId="8_{97E84CCC-6234-465C-AE6C-762AAC589669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDDE66D2-EE22-4573-8F46-539EED80084A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DD3C63B0-74E3-455B-9E64-045F09D85D0E}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{DD3C63B0-74E3-455B-9E64-045F09D85D0E}"/>
   </bookViews>
   <sheets>
     <sheet name="2012-2023" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="60">
   <si>
     <t>Togprodukt</t>
   </si>
@@ -333,7 +333,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
@@ -355,7 +355,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Komma" xfId="1" builtinId="3"/>
@@ -2853,7 +2852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE9A58E-6281-4D08-BF08-9517A14C48DB}">
-  <dimension ref="A1:I371"/>
+  <dimension ref="A1:I381"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="2"/>
@@ -12416,7 +12415,7 @@
       </c>
     </row>
     <row r="362" spans="1:8">
-      <c r="A362" s="21">
+      <c r="A362">
         <v>2026</v>
       </c>
       <c r="B362">
@@ -12442,7 +12441,7 @@
       </c>
     </row>
     <row r="363" spans="1:8">
-      <c r="A363" s="21">
+      <c r="A363">
         <v>2026</v>
       </c>
       <c r="B363">
@@ -12468,7 +12467,7 @@
       </c>
     </row>
     <row r="364" spans="1:8">
-      <c r="A364" s="21">
+      <c r="A364">
         <v>2026</v>
       </c>
       <c r="B364">
@@ -12494,7 +12493,7 @@
       </c>
     </row>
     <row r="365" spans="1:8">
-      <c r="A365" s="21">
+      <c r="A365">
         <v>2026</v>
       </c>
       <c r="B365">
@@ -12520,7 +12519,7 @@
       </c>
     </row>
     <row r="366" spans="1:8">
-      <c r="A366" s="21">
+      <c r="A366">
         <v>2026</v>
       </c>
       <c r="B366">
@@ -12546,7 +12545,7 @@
       </c>
     </row>
     <row r="367" spans="1:8">
-      <c r="A367" s="21">
+      <c r="A367">
         <v>2026</v>
       </c>
       <c r="B367">
@@ -12572,7 +12571,7 @@
       </c>
     </row>
     <row r="368" spans="1:8">
-      <c r="A368" s="21">
+      <c r="A368">
         <v>2026</v>
       </c>
       <c r="B368">
@@ -12598,7 +12597,7 @@
       </c>
     </row>
     <row r="369" spans="1:8">
-      <c r="A369" s="21">
+      <c r="A369">
         <v>2026</v>
       </c>
       <c r="B369">
@@ -12624,7 +12623,7 @@
       </c>
     </row>
     <row r="370" spans="1:8">
-      <c r="A370" s="21">
+      <c r="A370">
         <v>2026</v>
       </c>
       <c r="B370">
@@ -12650,7 +12649,7 @@
       </c>
     </row>
     <row r="371" spans="1:8">
-      <c r="A371" s="21">
+      <c r="A371">
         <v>2026</v>
       </c>
       <c r="B371">
@@ -12673,6 +12672,266 @@
       </c>
       <c r="H371">
         <v>59.271692000000002</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8">
+      <c r="A372" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B372" s="15">
+        <v>2</v>
+      </c>
+      <c r="C372" t="s">
+        <v>27</v>
+      </c>
+      <c r="D372" t="s">
+        <v>25</v>
+      </c>
+      <c r="E372" s="15">
+        <v>15763.276</v>
+      </c>
+      <c r="F372" s="15">
+        <v>15627.550000000003</v>
+      </c>
+      <c r="G372">
+        <v>10.31057</v>
+      </c>
+      <c r="H372">
+        <v>59.490316</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8">
+      <c r="A373" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B373" s="15">
+        <v>2</v>
+      </c>
+      <c r="C373" t="s">
+        <v>27</v>
+      </c>
+      <c r="D373" t="s">
+        <v>48</v>
+      </c>
+      <c r="E373" s="15">
+        <v>16887.088</v>
+      </c>
+      <c r="F373" s="15">
+        <v>17106.024999999994</v>
+      </c>
+      <c r="G373">
+        <v>10.031658</v>
+      </c>
+      <c r="H373">
+        <v>59.050156999999999</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8">
+      <c r="A374" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B374" s="15">
+        <v>2</v>
+      </c>
+      <c r="C374" t="s">
+        <v>27</v>
+      </c>
+      <c r="D374" t="s">
+        <v>49</v>
+      </c>
+      <c r="E374" s="15">
+        <v>18439.843999999997</v>
+      </c>
+      <c r="F374" s="15">
+        <v>18239.469999999998</v>
+      </c>
+      <c r="G374">
+        <v>9.6586879999999997</v>
+      </c>
+      <c r="H374">
+        <v>59.139364</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8">
+      <c r="A375" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B375" s="15">
+        <v>2</v>
+      </c>
+      <c r="C375" t="s">
+        <v>27</v>
+      </c>
+      <c r="D375" t="s">
+        <v>50</v>
+      </c>
+      <c r="E375" s="15">
+        <v>10779.126</v>
+      </c>
+      <c r="F375" s="15">
+        <v>10820.727999999997</v>
+      </c>
+      <c r="G375">
+        <v>10.204765999999999</v>
+      </c>
+      <c r="H375">
+        <v>59.585272000000003</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8">
+      <c r="A376" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B376" s="15">
+        <v>2</v>
+      </c>
+      <c r="C376" t="s">
+        <v>27</v>
+      </c>
+      <c r="D376" t="s">
+        <v>51</v>
+      </c>
+      <c r="E376" s="15">
+        <v>26003.548999999995</v>
+      </c>
+      <c r="F376" s="15">
+        <v>25985.699000000001</v>
+      </c>
+      <c r="G376">
+        <v>10.222754</v>
+      </c>
+      <c r="H376">
+        <v>59.135195000000003</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8">
+      <c r="A377" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B377" s="15">
+        <v>2</v>
+      </c>
+      <c r="C377" t="s">
+        <v>27</v>
+      </c>
+      <c r="D377" t="s">
+        <v>52</v>
+      </c>
+      <c r="E377" s="15">
+        <v>15232.963000000003</v>
+      </c>
+      <c r="F377" s="15">
+        <v>15074.470000000005</v>
+      </c>
+      <c r="G377">
+        <v>9.6035419999999991</v>
+      </c>
+      <c r="H377">
+        <v>59.219209999999997</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8">
+      <c r="A378" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B378" s="15">
+        <v>2</v>
+      </c>
+      <c r="C378" t="s">
+        <v>27</v>
+      </c>
+      <c r="D378" t="s">
+        <v>53</v>
+      </c>
+      <c r="E378" s="15">
+        <v>12107.071000000002</v>
+      </c>
+      <c r="F378" s="15">
+        <v>12213.746999999999</v>
+      </c>
+      <c r="G378">
+        <v>10.411125999999999</v>
+      </c>
+      <c r="H378">
+        <v>59.391182000000001</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8">
+      <c r="A379" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B379" s="15">
+        <v>2</v>
+      </c>
+      <c r="C379" t="s">
+        <v>27</v>
+      </c>
+      <c r="D379" t="s">
+        <v>54</v>
+      </c>
+      <c r="E379" s="15">
+        <v>7297.0609999999997</v>
+      </c>
+      <c r="F379" s="15">
+        <v>7054.0480000000007</v>
+      </c>
+      <c r="G379">
+        <v>10.300376999999999</v>
+      </c>
+      <c r="H379">
+        <v>59.221356999999998</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8">
+      <c r="A380" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B380" s="15">
+        <v>2</v>
+      </c>
+      <c r="C380" t="s">
+        <v>27</v>
+      </c>
+      <c r="D380" t="s">
+        <v>55</v>
+      </c>
+      <c r="E380" s="15">
+        <v>7755.3219999999983</v>
+      </c>
+      <c r="F380" s="15">
+        <v>7640.1989999999969</v>
+      </c>
+      <c r="G380">
+        <v>10.266265000000001</v>
+      </c>
+      <c r="H380">
+        <v>59.165590000000002</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8">
+      <c r="A381" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B381" s="15">
+        <v>2</v>
+      </c>
+      <c r="C381" t="s">
+        <v>27</v>
+      </c>
+      <c r="D381" t="s">
+        <v>56</v>
+      </c>
+      <c r="E381" s="15">
+        <v>49382.855999999992</v>
+      </c>
+      <c r="F381" s="15">
+        <v>50864.055000000008</v>
+      </c>
+      <c r="G381">
+        <v>10.409468</v>
+      </c>
+      <c r="H381">
+        <v>59.271925000000003</v>
       </c>
     </row>
   </sheetData>

--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Jernbanestatistikk_2012_2024.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Jernbanestatistikk_2012_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/kjetil_gunnerud_kristoffersen_vestfoldfylke_no/Documents/Dokumenter/GitHub2/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="687" documentId="8_{97E84CCC-6234-465C-AE6C-762AAC589669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDDE66D2-EE22-4573-8F46-539EED80084A}"/>
+  <xr:revisionPtr revIDLastSave="689" documentId="8_{97E84CCC-6234-465C-AE6C-762AAC589669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85F7A76D-D21B-42B6-9286-3CE2A934E711}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{DD3C63B0-74E3-455B-9E64-045F09D85D0E}"/>
+    <workbookView xWindow="-28905" yWindow="-3390" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{DD3C63B0-74E3-455B-9E64-045F09D85D0E}"/>
   </bookViews>
   <sheets>
     <sheet name="2012-2023" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="60">
   <si>
     <t>Togprodukt</t>
   </si>
@@ -333,7 +333,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
@@ -355,6 +355,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Komma" xfId="1" builtinId="3"/>
@@ -752,16 +753,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D0B74A-329A-43D4-ACFD-DCC824F63451}">
   <dimension ref="A1:N141"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.54296875" customWidth="1"/>
+    <col min="2" max="2" width="29.1796875" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -2852,18 +2853,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE9A58E-6281-4D08-BF08-9517A14C48DB}">
-  <dimension ref="A1:I381"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:I391"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="2"/>
-    <col min="2" max="2" width="17.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="2"/>
-    <col min="4" max="4" width="21.5703125" style="2" customWidth="1"/>
-    <col min="5" max="6" width="12.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="2"/>
+    <col min="2" max="2" width="17.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" style="2"/>
+    <col min="4" max="4" width="21.54296875" style="2" customWidth="1"/>
+    <col min="5" max="6" width="12.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" customWidth="1"/>
-    <col min="10" max="16384" width="11.42578125" style="2"/>
+    <col min="9" max="9" width="17.1796875" customWidth="1"/>
+    <col min="10" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -12931,6 +12932,266 @@
         <v>10.409468</v>
       </c>
       <c r="H381">
+        <v>59.271925000000003</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8">
+      <c r="A382" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B382" s="21">
+        <v>3</v>
+      </c>
+      <c r="C382" t="s">
+        <v>29</v>
+      </c>
+      <c r="D382" t="s">
+        <v>6</v>
+      </c>
+      <c r="E382" s="15">
+        <v>17985.091000000004</v>
+      </c>
+      <c r="F382" s="15">
+        <v>18463.501999999997</v>
+      </c>
+      <c r="G382">
+        <v>10.31057</v>
+      </c>
+      <c r="H382">
+        <v>59.490316</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8">
+      <c r="A383" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B383" s="21">
+        <v>3</v>
+      </c>
+      <c r="C383" t="s">
+        <v>29</v>
+      </c>
+      <c r="D383" t="s">
+        <v>7</v>
+      </c>
+      <c r="E383" s="15">
+        <v>18022.874000000003</v>
+      </c>
+      <c r="F383" s="15">
+        <v>18532.983000000004</v>
+      </c>
+      <c r="G383">
+        <v>10.031658</v>
+      </c>
+      <c r="H383">
+        <v>59.050156999999999</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8">
+      <c r="A384" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B384" s="21">
+        <v>3</v>
+      </c>
+      <c r="C384" t="s">
+        <v>29</v>
+      </c>
+      <c r="D384" t="s">
+        <v>8</v>
+      </c>
+      <c r="E384" s="15">
+        <v>18977.963</v>
+      </c>
+      <c r="F384" s="15">
+        <v>19674.811000000002</v>
+      </c>
+      <c r="G384">
+        <v>9.6586879999999997</v>
+      </c>
+      <c r="H384">
+        <v>59.139364</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8">
+      <c r="A385" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B385" s="21">
+        <v>3</v>
+      </c>
+      <c r="C385" t="s">
+        <v>29</v>
+      </c>
+      <c r="D385" t="s">
+        <v>9</v>
+      </c>
+      <c r="E385" s="15">
+        <v>12540.014999999998</v>
+      </c>
+      <c r="F385" s="15">
+        <v>12110.891999999996</v>
+      </c>
+      <c r="G385">
+        <v>10.204765999999999</v>
+      </c>
+      <c r="H385">
+        <v>59.585272000000003</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8">
+      <c r="A386" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B386" s="21">
+        <v>3</v>
+      </c>
+      <c r="C386" t="s">
+        <v>29</v>
+      </c>
+      <c r="D386" t="s">
+        <v>10</v>
+      </c>
+      <c r="E386" s="15">
+        <v>26953.010999999991</v>
+      </c>
+      <c r="F386" s="15">
+        <v>27424.282999999999</v>
+      </c>
+      <c r="G386">
+        <v>10.222754</v>
+      </c>
+      <c r="H386">
+        <v>59.135195000000003</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8">
+      <c r="A387" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B387" s="21">
+        <v>3</v>
+      </c>
+      <c r="C387" t="s">
+        <v>29</v>
+      </c>
+      <c r="D387" t="s">
+        <v>11</v>
+      </c>
+      <c r="E387" s="15">
+        <v>15779.802000000003</v>
+      </c>
+      <c r="F387" s="15">
+        <v>15911.046999999999</v>
+      </c>
+      <c r="G387">
+        <v>9.6035419999999991</v>
+      </c>
+      <c r="H387">
+        <v>59.219209999999997</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8">
+      <c r="A388" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B388" s="21">
+        <v>3</v>
+      </c>
+      <c r="C388" t="s">
+        <v>29</v>
+      </c>
+      <c r="D388" t="s">
+        <v>12</v>
+      </c>
+      <c r="E388" s="15">
+        <v>13196.145</v>
+      </c>
+      <c r="F388" s="15">
+        <v>13359.000999999998</v>
+      </c>
+      <c r="G388">
+        <v>10.411125999999999</v>
+      </c>
+      <c r="H388">
+        <v>59.391182000000001</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8">
+      <c r="A389" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B389" s="21">
+        <v>3</v>
+      </c>
+      <c r="C389" t="s">
+        <v>29</v>
+      </c>
+      <c r="D389" t="s">
+        <v>13</v>
+      </c>
+      <c r="E389" s="15">
+        <v>8168.9290000000001</v>
+      </c>
+      <c r="F389" s="15">
+        <v>8077.6289999999972</v>
+      </c>
+      <c r="G389">
+        <v>10.300376999999999</v>
+      </c>
+      <c r="H389">
+        <v>59.221356999999998</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8">
+      <c r="A390" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B390" s="21">
+        <v>3</v>
+      </c>
+      <c r="C390" t="s">
+        <v>29</v>
+      </c>
+      <c r="D390" t="s">
+        <v>14</v>
+      </c>
+      <c r="E390" s="15">
+        <v>7842.271999999999</v>
+      </c>
+      <c r="F390" s="15">
+        <v>8331.8009999999995</v>
+      </c>
+      <c r="G390">
+        <v>10.266265000000001</v>
+      </c>
+      <c r="H390">
+        <v>59.165590000000002</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8">
+      <c r="A391" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B391" s="21">
+        <v>3</v>
+      </c>
+      <c r="C391" t="s">
+        <v>29</v>
+      </c>
+      <c r="D391" t="s">
+        <v>15</v>
+      </c>
+      <c r="E391" s="15">
+        <v>51873.451999999976</v>
+      </c>
+      <c r="F391" s="15">
+        <v>54374.455999999998</v>
+      </c>
+      <c r="G391">
+        <v>10.409468</v>
+      </c>
+      <c r="H391">
         <v>59.271925000000003</v>
       </c>
     </row>
@@ -12951,9 +13212,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BAE721D-EEC0-4576-A3CE-F52737DC4230}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Jernbanestatistikk_2012_2024.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Jernbanestatistikk_2012_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/kjetil_gunnerud_kristoffersen_vestfoldfylke_no/Documents/Dokumenter/GitHub2/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="689" documentId="8_{97E84CCC-6234-465C-AE6C-762AAC589669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85F7A76D-D21B-42B6-9286-3CE2A934E711}"/>
+  <xr:revisionPtr revIDLastSave="695" documentId="8_{97E84CCC-6234-465C-AE6C-762AAC589669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3EEA69E-6D21-4496-BA8A-35066D02F47B}"/>
   <bookViews>
-    <workbookView xWindow="-28905" yWindow="-3390" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{DD3C63B0-74E3-455B-9E64-045F09D85D0E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DD3C63B0-74E3-455B-9E64-045F09D85D0E}"/>
   </bookViews>
   <sheets>
     <sheet name="2012-2023" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="60">
   <si>
     <t>Togprodukt</t>
   </si>
@@ -333,7 +333,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
@@ -355,7 +355,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Komma" xfId="1" builtinId="3"/>
@@ -753,16 +752,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D0B74A-329A-43D4-ACFD-DCC824F63451}">
   <dimension ref="A1:N141"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.54296875" customWidth="1"/>
-    <col min="2" max="2" width="29.1796875" customWidth="1"/>
-    <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -2853,18 +2852,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE9A58E-6281-4D08-BF08-9517A14C48DB}">
-  <dimension ref="A1:I391"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <dimension ref="A1:I411"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="2"/>
-    <col min="2" max="2" width="17.7265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.453125" style="2"/>
-    <col min="4" max="4" width="21.54296875" style="2" customWidth="1"/>
-    <col min="5" max="6" width="12.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="2"/>
+    <col min="2" max="2" width="17.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="2"/>
+    <col min="4" max="4" width="21.5703125" style="2" customWidth="1"/>
+    <col min="5" max="6" width="12.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="17.1796875" customWidth="1"/>
-    <col min="10" max="16384" width="11.453125" style="2"/>
+    <col min="9" max="9" width="17.140625" customWidth="1"/>
+    <col min="10" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -12939,7 +12938,7 @@
       <c r="A382" s="15">
         <v>2026</v>
       </c>
-      <c r="B382" s="21">
+      <c r="B382">
         <v>3</v>
       </c>
       <c r="C382" t="s">
@@ -12965,7 +12964,7 @@
       <c r="A383" s="15">
         <v>2026</v>
       </c>
-      <c r="B383" s="21">
+      <c r="B383">
         <v>3</v>
       </c>
       <c r="C383" t="s">
@@ -12991,7 +12990,7 @@
       <c r="A384" s="15">
         <v>2026</v>
       </c>
-      <c r="B384" s="21">
+      <c r="B384">
         <v>3</v>
       </c>
       <c r="C384" t="s">
@@ -13017,7 +13016,7 @@
       <c r="A385" s="15">
         <v>2026</v>
       </c>
-      <c r="B385" s="21">
+      <c r="B385">
         <v>3</v>
       </c>
       <c r="C385" t="s">
@@ -13043,7 +13042,7 @@
       <c r="A386" s="15">
         <v>2026</v>
       </c>
-      <c r="B386" s="21">
+      <c r="B386">
         <v>3</v>
       </c>
       <c r="C386" t="s">
@@ -13069,7 +13068,7 @@
       <c r="A387" s="15">
         <v>2026</v>
       </c>
-      <c r="B387" s="21">
+      <c r="B387">
         <v>3</v>
       </c>
       <c r="C387" t="s">
@@ -13095,7 +13094,7 @@
       <c r="A388" s="15">
         <v>2026</v>
       </c>
-      <c r="B388" s="21">
+      <c r="B388">
         <v>3</v>
       </c>
       <c r="C388" t="s">
@@ -13121,7 +13120,7 @@
       <c r="A389" s="15">
         <v>2026</v>
       </c>
-      <c r="B389" s="21">
+      <c r="B389">
         <v>3</v>
       </c>
       <c r="C389" t="s">
@@ -13147,7 +13146,7 @@
       <c r="A390" s="15">
         <v>2026</v>
       </c>
-      <c r="B390" s="21">
+      <c r="B390">
         <v>3</v>
       </c>
       <c r="C390" t="s">
@@ -13173,7 +13172,7 @@
       <c r="A391" s="15">
         <v>2026</v>
       </c>
-      <c r="B391" s="21">
+      <c r="B391">
         <v>3</v>
       </c>
       <c r="C391" t="s">
@@ -13192,6 +13191,526 @@
         <v>10.409468</v>
       </c>
       <c r="H391">
+        <v>59.271925000000003</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8">
+      <c r="A392" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B392">
+        <v>4</v>
+      </c>
+      <c r="C392" t="s">
+        <v>31</v>
+      </c>
+      <c r="D392" t="s">
+        <v>6</v>
+      </c>
+      <c r="E392" s="15">
+        <v>17853.337999999996</v>
+      </c>
+      <c r="F392" s="15">
+        <v>17936.532999999999</v>
+      </c>
+      <c r="G392">
+        <v>10.31057</v>
+      </c>
+      <c r="H392">
+        <v>59.490316</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8">
+      <c r="A393" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B393">
+        <v>4</v>
+      </c>
+      <c r="C393" t="s">
+        <v>31</v>
+      </c>
+      <c r="D393" t="s">
+        <v>7</v>
+      </c>
+      <c r="E393" s="15">
+        <v>17587.969999999998</v>
+      </c>
+      <c r="F393" s="15">
+        <v>17700.210000000003</v>
+      </c>
+      <c r="G393">
+        <v>10.031658</v>
+      </c>
+      <c r="H393">
+        <v>59.050156999999999</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8">
+      <c r="A394" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B394">
+        <v>4</v>
+      </c>
+      <c r="C394" t="s">
+        <v>31</v>
+      </c>
+      <c r="D394" t="s">
+        <v>8</v>
+      </c>
+      <c r="E394" s="15">
+        <v>18632.676999999996</v>
+      </c>
+      <c r="F394" s="15">
+        <v>18790.840000000004</v>
+      </c>
+      <c r="G394">
+        <v>9.6586879999999997</v>
+      </c>
+      <c r="H394">
+        <v>59.139364</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8">
+      <c r="A395" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B395">
+        <v>4</v>
+      </c>
+      <c r="C395" t="s">
+        <v>31</v>
+      </c>
+      <c r="D395" t="s">
+        <v>9</v>
+      </c>
+      <c r="E395" s="15">
+        <v>11897.651000000002</v>
+      </c>
+      <c r="F395" s="15">
+        <v>11443.466999999999</v>
+      </c>
+      <c r="G395">
+        <v>10.204765999999999</v>
+      </c>
+      <c r="H395">
+        <v>59.585272000000003</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8">
+      <c r="A396" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B396">
+        <v>4</v>
+      </c>
+      <c r="C396" t="s">
+        <v>31</v>
+      </c>
+      <c r="D396" t="s">
+        <v>10</v>
+      </c>
+      <c r="E396" s="15">
+        <v>27078.541999999998</v>
+      </c>
+      <c r="F396" s="15">
+        <v>26667.646000000008</v>
+      </c>
+      <c r="G396">
+        <v>10.222754</v>
+      </c>
+      <c r="H396">
+        <v>59.135195000000003</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8">
+      <c r="A397" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B397">
+        <v>4</v>
+      </c>
+      <c r="C397" t="s">
+        <v>31</v>
+      </c>
+      <c r="D397" t="s">
+        <v>11</v>
+      </c>
+      <c r="E397" s="15">
+        <v>15308.603999999999</v>
+      </c>
+      <c r="F397" s="15">
+        <v>15355.999999999998</v>
+      </c>
+      <c r="G397">
+        <v>9.6035419999999991</v>
+      </c>
+      <c r="H397">
+        <v>59.219209999999997</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8">
+      <c r="A398" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B398">
+        <v>4</v>
+      </c>
+      <c r="C398" t="s">
+        <v>31</v>
+      </c>
+      <c r="D398" t="s">
+        <v>12</v>
+      </c>
+      <c r="E398" s="15">
+        <v>13394.453999999998</v>
+      </c>
+      <c r="F398" s="15">
+        <v>12699.446</v>
+      </c>
+      <c r="G398">
+        <v>10.411125999999999</v>
+      </c>
+      <c r="H398">
+        <v>59.391182000000001</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8">
+      <c r="A399" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B399">
+        <v>4</v>
+      </c>
+      <c r="C399" t="s">
+        <v>31</v>
+      </c>
+      <c r="D399" t="s">
+        <v>13</v>
+      </c>
+      <c r="E399" s="15">
+        <v>7660.5440000000008</v>
+      </c>
+      <c r="F399" s="15">
+        <v>7311.0620000000008</v>
+      </c>
+      <c r="G399">
+        <v>10.300376999999999</v>
+      </c>
+      <c r="H399">
+        <v>59.221356999999998</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8">
+      <c r="A400" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B400">
+        <v>4</v>
+      </c>
+      <c r="C400" t="s">
+        <v>31</v>
+      </c>
+      <c r="D400" t="s">
+        <v>14</v>
+      </c>
+      <c r="E400" s="15">
+        <v>8905.3719999999994</v>
+      </c>
+      <c r="F400" s="15">
+        <v>8326.4019999999982</v>
+      </c>
+      <c r="G400">
+        <v>10.266265000000001</v>
+      </c>
+      <c r="H400">
+        <v>59.165590000000002</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8">
+      <c r="A401" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B401">
+        <v>4</v>
+      </c>
+      <c r="C401" t="s">
+        <v>31</v>
+      </c>
+      <c r="D401" t="s">
+        <v>15</v>
+      </c>
+      <c r="E401" s="15">
+        <v>51277.114999999976</v>
+      </c>
+      <c r="F401" s="15">
+        <v>51613.572000000015</v>
+      </c>
+      <c r="G401">
+        <v>10.409468</v>
+      </c>
+      <c r="H401">
+        <v>59.271925000000003</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8">
+      <c r="A402" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B402">
+        <v>5</v>
+      </c>
+      <c r="C402" t="s">
+        <v>33</v>
+      </c>
+      <c r="D402" t="s">
+        <v>6</v>
+      </c>
+      <c r="E402" s="15">
+        <v>17711.867000000002</v>
+      </c>
+      <c r="F402" s="15">
+        <v>17631.956999999999</v>
+      </c>
+      <c r="G402">
+        <v>10.31057</v>
+      </c>
+      <c r="H402">
+        <v>59.490316</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8">
+      <c r="A403" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B403">
+        <v>5</v>
+      </c>
+      <c r="C403" t="s">
+        <v>33</v>
+      </c>
+      <c r="D403" t="s">
+        <v>7</v>
+      </c>
+      <c r="E403" s="15">
+        <v>20645.476999999999</v>
+      </c>
+      <c r="F403" s="15">
+        <v>20352.218999999997</v>
+      </c>
+      <c r="G403">
+        <v>10.031658</v>
+      </c>
+      <c r="H403">
+        <v>59.050156999999999</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8">
+      <c r="A404" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B404">
+        <v>5</v>
+      </c>
+      <c r="C404" t="s">
+        <v>33</v>
+      </c>
+      <c r="D404" t="s">
+        <v>8</v>
+      </c>
+      <c r="E404" s="15">
+        <v>20059.190000000002</v>
+      </c>
+      <c r="F404" s="15">
+        <v>20193.807999999997</v>
+      </c>
+      <c r="G404">
+        <v>9.6586879999999997</v>
+      </c>
+      <c r="H404">
+        <v>59.139364</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8">
+      <c r="A405" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B405">
+        <v>5</v>
+      </c>
+      <c r="C405" t="s">
+        <v>33</v>
+      </c>
+      <c r="D405" t="s">
+        <v>9</v>
+      </c>
+      <c r="E405" s="15">
+        <v>12668.223000000002</v>
+      </c>
+      <c r="F405" s="15">
+        <v>12512.161</v>
+      </c>
+      <c r="G405">
+        <v>10.204765999999999</v>
+      </c>
+      <c r="H405">
+        <v>59.585272000000003</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8">
+      <c r="A406" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B406">
+        <v>5</v>
+      </c>
+      <c r="C406" t="s">
+        <v>33</v>
+      </c>
+      <c r="D406" t="s">
+        <v>10</v>
+      </c>
+      <c r="E406" s="15">
+        <v>30430.189999999991</v>
+      </c>
+      <c r="F406" s="15">
+        <v>30477.260000000006</v>
+      </c>
+      <c r="G406">
+        <v>10.222754</v>
+      </c>
+      <c r="H406">
+        <v>59.135195000000003</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8">
+      <c r="A407" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B407">
+        <v>5</v>
+      </c>
+      <c r="C407" t="s">
+        <v>33</v>
+      </c>
+      <c r="D407" t="s">
+        <v>11</v>
+      </c>
+      <c r="E407" s="15">
+        <v>17210.066999999999</v>
+      </c>
+      <c r="F407" s="15">
+        <v>17087.804</v>
+      </c>
+      <c r="G407">
+        <v>9.6035419999999991</v>
+      </c>
+      <c r="H407">
+        <v>59.219209999999997</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8">
+      <c r="A408" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B408">
+        <v>5</v>
+      </c>
+      <c r="C408" t="s">
+        <v>33</v>
+      </c>
+      <c r="D408" t="s">
+        <v>12</v>
+      </c>
+      <c r="E408" s="15">
+        <v>13179.010999999997</v>
+      </c>
+      <c r="F408" s="15">
+        <v>13188.174999999999</v>
+      </c>
+      <c r="G408">
+        <v>10.411125999999999</v>
+      </c>
+      <c r="H408">
+        <v>59.391182000000001</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8">
+      <c r="A409" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B409">
+        <v>5</v>
+      </c>
+      <c r="C409" t="s">
+        <v>33</v>
+      </c>
+      <c r="D409" t="s">
+        <v>13</v>
+      </c>
+      <c r="E409" s="15">
+        <v>8475.6139999999978</v>
+      </c>
+      <c r="F409" s="15">
+        <v>8599.2160000000003</v>
+      </c>
+      <c r="G409">
+        <v>10.300376999999999</v>
+      </c>
+      <c r="H409">
+        <v>59.221356999999998</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8">
+      <c r="A410" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B410">
+        <v>5</v>
+      </c>
+      <c r="C410" t="s">
+        <v>33</v>
+      </c>
+      <c r="D410" t="s">
+        <v>14</v>
+      </c>
+      <c r="E410" s="15">
+        <v>9076.0909999999985</v>
+      </c>
+      <c r="F410" s="15">
+        <v>9133.1260000000002</v>
+      </c>
+      <c r="G410">
+        <v>10.266265000000001</v>
+      </c>
+      <c r="H410">
+        <v>59.165590000000002</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8">
+      <c r="A411" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B411">
+        <v>5</v>
+      </c>
+      <c r="C411" t="s">
+        <v>33</v>
+      </c>
+      <c r="D411" t="s">
+        <v>15</v>
+      </c>
+      <c r="E411" s="15">
+        <v>55785.824000000001</v>
+      </c>
+      <c r="F411" s="15">
+        <v>56849.459000000003</v>
+      </c>
+      <c r="G411">
+        <v>10.409468</v>
+      </c>
+      <c r="H411">
         <v>59.271925000000003</v>
       </c>
     </row>
@@ -13212,9 +13731,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BAE721D-EEC0-4576-A3CE-F52737DC4230}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Jernbanestatistikk_2012_2024.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Jernbanestatistikk_2012_2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="695" documentId="8_{97E84CCC-6234-465C-AE6C-762AAC589669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3EEA69E-6D21-4496-BA8A-35066D02F47B}"/>
+  <xr:revisionPtr revIDLastSave="704" documentId="8_{97E84CCC-6234-465C-AE6C-762AAC589669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCC12E55-92C9-41BD-A2EF-76C418CDBD93}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DD3C63B0-74E3-455B-9E64-045F09D85D0E}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="60">
   <si>
     <t>Togprodukt</t>
   </si>
@@ -2852,7 +2852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE9A58E-6281-4D08-BF08-9517A14C48DB}">
-  <dimension ref="A1:I411"/>
+  <dimension ref="A1:I431"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="2"/>
@@ -13711,6 +13711,526 @@
         <v>10.409468</v>
       </c>
       <c r="H411">
+        <v>59.271925000000003</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8">
+      <c r="A412" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B412">
+        <v>6</v>
+      </c>
+      <c r="C412" t="s">
+        <v>35</v>
+      </c>
+      <c r="D412" t="s">
+        <v>6</v>
+      </c>
+      <c r="E412" s="15">
+        <v>19373.491000000013</v>
+      </c>
+      <c r="F412" s="15">
+        <v>18807.744999999999</v>
+      </c>
+      <c r="G412">
+        <v>10.31057</v>
+      </c>
+      <c r="H412">
+        <v>59.490316</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8">
+      <c r="A413" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B413">
+        <v>6</v>
+      </c>
+      <c r="C413" t="s">
+        <v>35</v>
+      </c>
+      <c r="D413" t="s">
+        <v>7</v>
+      </c>
+      <c r="E413" s="15">
+        <v>21545.300000000007</v>
+      </c>
+      <c r="F413" s="15">
+        <v>22832.944000000018</v>
+      </c>
+      <c r="G413">
+        <v>10.031658</v>
+      </c>
+      <c r="H413">
+        <v>59.050156999999999</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8">
+      <c r="A414" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B414">
+        <v>6</v>
+      </c>
+      <c r="C414" t="s">
+        <v>35</v>
+      </c>
+      <c r="D414" t="s">
+        <v>8</v>
+      </c>
+      <c r="E414" s="15">
+        <v>22626.014999999999</v>
+      </c>
+      <c r="F414" s="15">
+        <v>22471.969999999987</v>
+      </c>
+      <c r="G414">
+        <v>9.6586879999999997</v>
+      </c>
+      <c r="H414">
+        <v>59.139364</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8">
+      <c r="A415" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B415">
+        <v>6</v>
+      </c>
+      <c r="C415" t="s">
+        <v>35</v>
+      </c>
+      <c r="D415" t="s">
+        <v>9</v>
+      </c>
+      <c r="E415" s="15">
+        <v>13059.395</v>
+      </c>
+      <c r="F415" s="15">
+        <v>12580.774000000001</v>
+      </c>
+      <c r="G415">
+        <v>10.204765999999999</v>
+      </c>
+      <c r="H415">
+        <v>59.585272000000003</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8">
+      <c r="A416" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B416">
+        <v>6</v>
+      </c>
+      <c r="C416" t="s">
+        <v>35</v>
+      </c>
+      <c r="D416" t="s">
+        <v>10</v>
+      </c>
+      <c r="E416" s="15">
+        <v>33560.673000000024</v>
+      </c>
+      <c r="F416" s="15">
+        <v>33659.114000000031</v>
+      </c>
+      <c r="G416">
+        <v>10.222754</v>
+      </c>
+      <c r="H416">
+        <v>59.135195000000003</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8">
+      <c r="A417" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B417">
+        <v>6</v>
+      </c>
+      <c r="C417" t="s">
+        <v>35</v>
+      </c>
+      <c r="D417" t="s">
+        <v>11</v>
+      </c>
+      <c r="E417" s="15">
+        <v>18312.466</v>
+      </c>
+      <c r="F417" s="15">
+        <v>18550.804000000004</v>
+      </c>
+      <c r="G417">
+        <v>9.6035419999999991</v>
+      </c>
+      <c r="H417">
+        <v>59.219209999999997</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8">
+      <c r="A418" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B418">
+        <v>6</v>
+      </c>
+      <c r="C418" t="s">
+        <v>35</v>
+      </c>
+      <c r="D418" t="s">
+        <v>12</v>
+      </c>
+      <c r="E418" s="15">
+        <v>14425.670999999991</v>
+      </c>
+      <c r="F418" s="15">
+        <v>14687.433999999997</v>
+      </c>
+      <c r="G418">
+        <v>10.411125999999999</v>
+      </c>
+      <c r="H418">
+        <v>59.391182000000001</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8">
+      <c r="A419" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B419">
+        <v>6</v>
+      </c>
+      <c r="C419" t="s">
+        <v>35</v>
+      </c>
+      <c r="D419" t="s">
+        <v>13</v>
+      </c>
+      <c r="E419" s="15">
+        <v>8801.2410000000054</v>
+      </c>
+      <c r="F419" s="15">
+        <v>8809.1600000000053</v>
+      </c>
+      <c r="G419">
+        <v>10.300376999999999</v>
+      </c>
+      <c r="H419">
+        <v>59.221356999999998</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8">
+      <c r="A420" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B420">
+        <v>6</v>
+      </c>
+      <c r="C420" t="s">
+        <v>35</v>
+      </c>
+      <c r="D420" t="s">
+        <v>14</v>
+      </c>
+      <c r="E420" s="15">
+        <v>9270.8300000000017</v>
+      </c>
+      <c r="F420" s="15">
+        <v>9677.8410000000022</v>
+      </c>
+      <c r="G420">
+        <v>10.266265000000001</v>
+      </c>
+      <c r="H420">
+        <v>59.165590000000002</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8">
+      <c r="A421" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B421">
+        <v>6</v>
+      </c>
+      <c r="C421" t="s">
+        <v>35</v>
+      </c>
+      <c r="D421" t="s">
+        <v>15</v>
+      </c>
+      <c r="E421" s="15">
+        <v>62876.303000000007</v>
+      </c>
+      <c r="F421" s="15">
+        <v>63385.881000000023</v>
+      </c>
+      <c r="G421">
+        <v>10.409468</v>
+      </c>
+      <c r="H421">
+        <v>59.271925000000003</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8">
+      <c r="A422" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B422">
+        <v>7</v>
+      </c>
+      <c r="C422" t="s">
+        <v>37</v>
+      </c>
+      <c r="D422" t="s">
+        <v>6</v>
+      </c>
+      <c r="E422" s="15">
+        <v>11468.261999999995</v>
+      </c>
+      <c r="F422" s="15">
+        <v>11264.169999999995</v>
+      </c>
+      <c r="G422">
+        <v>10.31057</v>
+      </c>
+      <c r="H422">
+        <v>59.490316</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8">
+      <c r="A423" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B423">
+        <v>7</v>
+      </c>
+      <c r="C423" t="s">
+        <v>37</v>
+      </c>
+      <c r="D423" t="s">
+        <v>7</v>
+      </c>
+      <c r="E423" s="15">
+        <v>16008.197000000022</v>
+      </c>
+      <c r="F423" s="15">
+        <v>16338.674999999999</v>
+      </c>
+      <c r="G423">
+        <v>10.031658</v>
+      </c>
+      <c r="H423">
+        <v>59.050156999999999</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8">
+      <c r="A424" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B424">
+        <v>7</v>
+      </c>
+      <c r="C424" t="s">
+        <v>37</v>
+      </c>
+      <c r="D424" t="s">
+        <v>8</v>
+      </c>
+      <c r="E424" s="15">
+        <v>15693.043000000001</v>
+      </c>
+      <c r="F424" s="15">
+        <v>14946.225000000002</v>
+      </c>
+      <c r="G424">
+        <v>9.6586879999999997</v>
+      </c>
+      <c r="H424">
+        <v>59.139364</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8">
+      <c r="A425" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B425">
+        <v>7</v>
+      </c>
+      <c r="C425" t="s">
+        <v>37</v>
+      </c>
+      <c r="D425" t="s">
+        <v>9</v>
+      </c>
+      <c r="E425" s="15">
+        <v>7090.5769999999957</v>
+      </c>
+      <c r="F425" s="15">
+        <v>7245.7060000000038</v>
+      </c>
+      <c r="G425">
+        <v>10.204765999999999</v>
+      </c>
+      <c r="H425">
+        <v>59.585272000000003</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8">
+      <c r="A426" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B426">
+        <v>7</v>
+      </c>
+      <c r="C426" t="s">
+        <v>37</v>
+      </c>
+      <c r="D426" t="s">
+        <v>10</v>
+      </c>
+      <c r="E426" s="15">
+        <v>21991.61099999999</v>
+      </c>
+      <c r="F426" s="15">
+        <v>21309.760999999991</v>
+      </c>
+      <c r="G426">
+        <v>10.222754</v>
+      </c>
+      <c r="H426">
+        <v>59.135195000000003</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8">
+      <c r="A427" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B427">
+        <v>7</v>
+      </c>
+      <c r="C427" t="s">
+        <v>37</v>
+      </c>
+      <c r="D427" t="s">
+        <v>11</v>
+      </c>
+      <c r="E427" s="15">
+        <v>13737.669999999995</v>
+      </c>
+      <c r="F427" s="15">
+        <v>13047.589999999997</v>
+      </c>
+      <c r="G427">
+        <v>9.6035419999999991</v>
+      </c>
+      <c r="H427">
+        <v>59.219209999999997</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8">
+      <c r="A428" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B428">
+        <v>7</v>
+      </c>
+      <c r="C428" t="s">
+        <v>37</v>
+      </c>
+      <c r="D428" t="s">
+        <v>12</v>
+      </c>
+      <c r="E428" s="15">
+        <v>7030.0909999999976</v>
+      </c>
+      <c r="F428" s="15">
+        <v>6938.9600000000028</v>
+      </c>
+      <c r="G428">
+        <v>10.411125999999999</v>
+      </c>
+      <c r="H428">
+        <v>59.391182000000001</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8">
+      <c r="A429" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B429">
+        <v>7</v>
+      </c>
+      <c r="C429" t="s">
+        <v>37</v>
+      </c>
+      <c r="D429" t="s">
+        <v>13</v>
+      </c>
+      <c r="E429" s="15">
+        <v>5907.6789999999974</v>
+      </c>
+      <c r="F429" s="15">
+        <v>5863.8599999999988</v>
+      </c>
+      <c r="G429">
+        <v>10.300376999999999</v>
+      </c>
+      <c r="H429">
+        <v>59.221356999999998</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8">
+      <c r="A430" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B430">
+        <v>7</v>
+      </c>
+      <c r="C430" t="s">
+        <v>37</v>
+      </c>
+      <c r="D430" t="s">
+        <v>14</v>
+      </c>
+      <c r="E430" s="15">
+        <v>6499.5209999999952</v>
+      </c>
+      <c r="F430" s="15">
+        <v>6499.4949999999963</v>
+      </c>
+      <c r="G430">
+        <v>10.266265000000001</v>
+      </c>
+      <c r="H430">
+        <v>59.165590000000002</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8">
+      <c r="A431" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B431">
+        <v>7</v>
+      </c>
+      <c r="C431" t="s">
+        <v>37</v>
+      </c>
+      <c r="D431" t="s">
+        <v>15</v>
+      </c>
+      <c r="E431" s="15">
+        <v>39421.945000000007</v>
+      </c>
+      <c r="F431" s="15">
+        <v>40051.250000000029</v>
+      </c>
+      <c r="G431">
+        <v>10.409468</v>
+      </c>
+      <c r="H431">
         <v>59.271925000000003</v>
       </c>
     </row>
